--- a/pacjenci/MARTA ZMUDA.xlsx
+++ b/pacjenci/MARTA ZMUDA.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -630,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/MARTA ZMUDA.xlsx
+++ b/pacjenci/MARTA ZMUDA.xlsx
@@ -413,235 +413,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>14.05.2020</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina typ klasyczny NS. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 64 min od podania 18F-FDG. Glikemia: 102 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywny metabolicznie, pakiet węzłów chłonnych szyjnych grupy 4 po stronie lewej wielkości 30x18x33 mm wg PET SUV max 11,7  [Im fuz. 83]. Aktywny metabolicznie węzeł chłonny nadobojczykowy lewy wielkości 10 mm SUV max 6,0 [Im fuz. 88]. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie pojedyncze i spakietowane węzły chłonne: - przytchawicze górne lewe wielkości 22x24x29 mm SUV max 10,1 [Im fuz. 92] - śródpiersiowe przednie lewe i lewobocznie od łuku aorty wielkości do 39x48x65 mm SUV max do 10,4 [Im CT 278] - śródpiersiowe najwyższe wielkości 12 mm wg PET SUV max 7,6  [Im fuz. 98] Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku, zwłaszcza w jego dnie SUV max do  6,4- w pierwszej kolejności o charakterze odczynowo- zapalnym. Rozlanie wzmożony metabolizm FDG w śledzionie SUV max do 3,1. Wzmożony metabolizm FDG w topografii obu przydatków SUV max do 7,0 oraz w endometrium macicy SUV max do 7,8- w pierwszej kolejności o charakterze czynnościowym (OM 04.05.2020) Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Dyskopatia L5/S1, niezrośnięte jądro kostnienia L5.   Inne: Pobudzenie metaboliczne w tkance brunatnej szyi i klatki piersiowej.  Wartości referencyjne: MBPS SUVmax 1,4 Prawy płat wątroby SUVmax do 2,8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18 F-FDG uwidoczniono obecność aktywnej metabolicznie choroby chłoniakowej z zajęciem węzłów chłonnych szyi i śródpiersia- AnnArbor II. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>11.7</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>27.07.2020</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina typ klasyczny NS. Ocena wczesnej odpowiedzi na stosowane leczenie.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 86mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Rozlana, symetryczna aktywność metaboliczna w topografii jamy nosowej oraz struktur pierścienia Waldeyera, SUV max do 5,9. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. W prawej zatoce szczękowej pogrubienie śluzówki.  Klatka piersiowa i śródpiersie: Mierne pobudzenie metaboliczne w węzłach chłonnych lewobocznie od łuku aorty wielkości do 27x43x56mm, SUV max do 2,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Rozlanie wzmożony metabolizm FDG w żołądku, zwłaszcza w jego dnie SUV max do 3,6 - w pierwszej kolejności o charakterze odczynowym. Rozlanie wzmożony metabolizm FDG w esicy, SUV max do 6,3 - w pierwszej kolejności o charakterze czynnościowym. Wzmożony metabolizm FDG w topografii  w endometrium macicy SUV max do 4,2 w pierwszej kolejności o charakterze czynnościowym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W miednicy mniejszej do tyłu od przydatków lewych widoczny okrągły obszar płynowy - torbiel ? średnicy 19mm  - do oceny w USG - TV. W  jamie Douglasa widoczna jest niewielka ilość płynu.   Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym objętym badaniem - w pierwszej kolejności związany z prowadzonym leczeniem SUV max 3,3. Dyskopatia L5/S1, niezrośnięte jądro kostnienia L5.   Wartości referencyjne: MBPS SUVmax 2,0 Prawy płat wątroby SUVmax do 2,7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18 F-FDG uwidoczniono dobrą odpowiedź choroby chłoniakowej na zastosowanie leczenie.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>6.3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>10.12.2020</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina typ klasyczny NS. Ocena remisji choroby po zakończeniu ChTh. W planie ew. kwalifikacja do IFRT.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 98 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywny metabolicznie pakiet węzłów chłonnych lewobocznie od łuku aorty wielkości ok 22x39x46 mm (SUV max 1,7). W przyleganiu widoczne sa drobne węzły chłonne wielkości do 10mm. Drobne zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W grzbietowo-lewobocznej części miednicy, w topografii pętli jelitowych oraz nieco do tyłu od przydatków lewych widoczny owalny obszar płynowy -wielkości 17x25 mm [Im CT 635] -  torbiel ?  - do oceny w USG t.v. i do kontroli ginekologicznej.  Układ kostny: Rozlanie wzmożony metabolizm FDG w układzie kostnym objętym badaniem  SUV max do 4,9- w pierwszej kolejności związany z prowadzonym leczeniem. Drobne zmiany zwyrodnieniowe kręgosłupa. Dyskopatia na poziomie L5/S1. Odszczepione jądro kostnienia w przednio-górnej części trzonu L5.  Os sacrum arcuatum.  Inne: Wzmożony metabolizm FDG w tkance brunatnej szyi i klatki piersiowej.  Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18 F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Nieaktywny metabolicznie pakiet węzłów chłonnych położony lewobocznie od łuku aorty- do dalszej kontroli. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.9</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>01.06.2021</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina typ klasyczny NS. Ocena remisji choroby po zakończeniu ChTh i  IFRT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 61min od podania 18F-FDG. Glikemia: 97mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetryczna aktywność metaboliczna w strukturach pierścienia Waldeyera, SUV max do 4,9. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aplazja zatok czołowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieaktywny metabolicznie pakiet węzłów chłonnych lewobocznie od łuku aorty wielkości ok 22x39mm - jak poprzednio. Przytchawiczo widoczny węzeł 16x19mm, kolejny 17x9mm lewobocznie od t. szyjnej wspólnej lewej  - jak poprzednio W przyleganiu widoczne są drobne węzły chłonne wielkości do 8mm. Drobne zmiany włókniste nadprzeponowo w płucu lewym.  Brzuch i miednica: Rozlana, mierna aktywność metaboliczna w topografii ścian żołądka, SUV max do 5,9 - w pierwszej kolejności czynnościowe. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. W grzbietowo-lewobocznej części miednicy, w topografii pętli jelitowych oraz nieco do tyłu od przydatków lewych widoczny owalny obszar płynowy -wielkości 20x22mm [Im CT 656] -  torbiel ?  - do oceny w USG t.v. i do kontroli ginekologicznej.  Układ kostny: Fizjologiczny  metabolizm FDG w układzie kostnym objętym badaniem. Drobne zmiany zwyrodnieniowe kręgosłupa. Dyskopatia na poziomie L5/S1. Odszczepione jądro kostnienia w przednio-górnej części trzonu L5. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax 1,4; Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18 F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Masa resztkowa - do dalszej kontroli.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.9</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>
